--- a/data/trending_integrated_20260914_09.xlsx
+++ b/data/trending_integrated_20260914_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15530</v>
+        <v>15380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+6.30%</t>
+          <t>+5.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.97</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="H2" t="n">
         <v>1.17</v>
@@ -601,7 +601,7 @@
         <v>15420</v>
       </c>
       <c r="L2" t="n">
-        <v>15640</v>
+        <v>16510</v>
       </c>
       <c r="M2" t="n">
         <v>15300</v>
@@ -610,7 +610,7 @@
         <v>3.14</v>
       </c>
       <c r="O2" t="n">
-        <v>8959984415</v>
+        <v>55776812710</v>
       </c>
       <c r="P2" t="n">
         <v>36200</v>
@@ -655,60 +655,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1718000</v>
+        <v>14110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.08</v>
+        <v>-0.62</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>486</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>2098</v>
+        <v>156</v>
       </c>
       <c r="H3" t="n">
-        <v>50.47</v>
+        <v>1.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1812000</v>
+        <v>14150</v>
       </c>
       <c r="K3" t="n">
-        <v>1707000</v>
+        <v>13850</v>
       </c>
       <c r="L3" t="n">
-        <v>1724000</v>
+        <v>14310</v>
       </c>
       <c r="M3" t="n">
-        <v>1707000</v>
+        <v>13800</v>
       </c>
       <c r="N3" t="n">
-        <v>50.55</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>413414480000</v>
+        <v>13948663695</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q3" t="n">
-        <v>325000</v>
+        <v>1272</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국, 일본 금리 인상 가능성과 트럼프 관련 불확실성으로 인한 하락 기대감 속, 월스트리트저널의 반도체 수급 폭발 전망 뉴스가 혼재.</t>
+          <t>대한광통신, AI 관련 광통신 기술 성장 기대감 및 프로그램 매수세 유입 속 상승 전망. 금리 동결 기대감도 긍정적 요인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,18 +727,294 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['금리 인상', '반도체 수급', 'HBM']</t>
+          <t>['광통신 기술', '프로그램 매수', '금리 동결']</t>
         </is>
       </c>
       <c r="X3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>89200</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-1.76%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E4" t="n">
+        <v>95</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66</v>
+      </c>
+      <c r="G4" t="n">
+        <v>392</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>90800</v>
+      </c>
+      <c r="K4" t="n">
+        <v>89800</v>
+      </c>
+      <c r="L4" t="n">
+        <v>90400</v>
+      </c>
+      <c r="M4" t="n">
+        <v>87800</v>
+      </c>
+      <c r="N4" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="O4" t="n">
+        <v>42773849150</v>
+      </c>
+      <c r="P4" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>두산에너빌리티, 국제 유가 상승 및 한미 정부 지원 기대감으로 인한 상승 가능성 언급. 다만, 미국 원전주 폭락 소식은 부담.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['국제 유가', '원전주', '정부 지원']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>251000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-3.28%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>702</v>
+      </c>
+      <c r="F5" t="n">
+        <v>442</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2277</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>259500</v>
+      </c>
+      <c r="K5" t="n">
+        <v>249500</v>
+      </c>
+      <c r="L5" t="n">
+        <v>251500</v>
+      </c>
+      <c r="M5" t="n">
+        <v>249000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="O5" t="n">
+        <v>486442349000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>75900</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>삼성전자, 지정학적 리스크 및 AI 속도 조절론 속 외국인 매도세 동반 하락. 다만, 글로벌 증시 변동성과 연동되는 모습.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['지정학적 리스크', 'AI 속도론', '외국인 매도']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1718000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-5.19%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>477</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1686</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>853819433000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>325000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 나스닥 선물 급락 및 반도체 시세 종료 우려 속 부정적 전망 지배적.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['나스닥 선물', '반도체 시세', '몰락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>70</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20260914_09.xlsx
+++ b/data/trending_integrated_20260914_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15380</v>
+        <v>18050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+5.27%</t>
+          <t>+12.39%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.97</v>
+        <v>0.31</v>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>321</v>
+        <v>71</v>
       </c>
       <c r="H2" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>14610</v>
+        <v>16060</v>
       </c>
       <c r="K2" t="n">
-        <v>15420</v>
+        <v>16780</v>
       </c>
       <c r="L2" t="n">
-        <v>16510</v>
+        <v>18610</v>
       </c>
       <c r="M2" t="n">
-        <v>15300</v>
+        <v>16230</v>
       </c>
       <c r="N2" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="O2" t="n">
-        <v>55776812710</v>
+        <v>153877047085</v>
       </c>
       <c r="P2" t="n">
-        <v>36200</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>8920</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 폭등 소식에 따른 상승 기대감.</t>
+          <t>AI 개발 속도 조절론에 따른 변동성 속에서, 사이버 보안 관련주의 부각 및 긍정적 주가 흐름 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['국제 유가', '호르무즈 해협', '회담 연기']</t>
+          <t>['AI', '사이버 보안', '상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14110</v>
+        <v>8710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+5.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>156</v>
+        <v>283</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14150</v>
+        <v>8290</v>
       </c>
       <c r="K3" t="n">
-        <v>13850</v>
+        <v>8100</v>
       </c>
       <c r="L3" t="n">
-        <v>14310</v>
+        <v>8900</v>
       </c>
       <c r="M3" t="n">
-        <v>13800</v>
+        <v>8060</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="O3" t="n">
-        <v>13948663695</v>
+        <v>8385544075</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>21500</v>
       </c>
       <c r="Q3" t="n">
-        <v>1272</v>
+        <v>2300</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대한광통신, AI 관련 광통신 기술 성장 기대감 및 프로그램 매수세 유입 속 상승 전망. 금리 동결 기대감도 긍정적 요인.</t>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 소식 기반, 투자주의 해제 후 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신 기술', '프로그램 매수', '금리 동결']</t>
+          <t>['항암', '신약', '심포지엄']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89200</v>
+        <v>15150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+3.70%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-1.97</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>392</v>
+        <v>335</v>
       </c>
       <c r="H4" t="n">
-        <v>23.56</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>90800</v>
+        <v>14610</v>
       </c>
       <c r="K4" t="n">
-        <v>89800</v>
+        <v>15420</v>
       </c>
       <c r="L4" t="n">
-        <v>90400</v>
+        <v>16510</v>
       </c>
       <c r="M4" t="n">
-        <v>87800</v>
+        <v>15100</v>
       </c>
       <c r="N4" t="n">
-        <v>23.59</v>
+        <v>3.14</v>
       </c>
       <c r="O4" t="n">
-        <v>42773849150</v>
+        <v>67030269340</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 국제 유가 상승 및 한미 정부 지원 기대감으로 인한 상승 가능성 언급. 다만, 미국 원전주 폭락 소식은 부담.</t>
+          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 폭등 소식에 따른 상승 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제 유가', '원전주', '정부 지원']</t>
+          <t>['국제 유가', '호르무즈 해협', '회담 연기']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>251000</v>
+        <v>14050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="E5" t="n">
-        <v>702</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>442</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>2277</v>
+        <v>174</v>
       </c>
       <c r="H5" t="n">
-        <v>46.64</v>
+        <v>1.88</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>259500</v>
+        <v>14150</v>
       </c>
       <c r="K5" t="n">
-        <v>249500</v>
+        <v>13850</v>
       </c>
       <c r="L5" t="n">
-        <v>251500</v>
+        <v>14310</v>
       </c>
       <c r="M5" t="n">
-        <v>249000</v>
+        <v>13800</v>
       </c>
       <c r="N5" t="n">
-        <v>46.71</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>486442349000</v>
+        <v>19556056885</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>75900</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, 지정학적 리스크 및 AI 속도 조절론 속 외국인 매도세 동반 하락. 다만, 글로벌 증시 변동성과 연동되는 모습.</t>
+          <t>GPU 확보 관련 긍정 뉴스에 힘입어 기술력 부각, 프로그램 매수세 유입 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', 'AI 속도론', '외국인 매도']</t>
+          <t>['GPU', '광통신', 'AIDC']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1718000</v>
+        <v>88500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>477</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>1686</v>
+        <v>406</v>
       </c>
       <c r="H6" t="n">
-        <v>50.47</v>
+        <v>23.56</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,58 +963,242 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1812000</v>
+        <v>90800</v>
       </c>
       <c r="K6" t="n">
-        <v>1707000</v>
+        <v>89800</v>
       </c>
       <c r="L6" t="n">
-        <v>1729000</v>
+        <v>90400</v>
       </c>
       <c r="M6" t="n">
-        <v>1707000</v>
+        <v>87800</v>
       </c>
       <c r="N6" t="n">
-        <v>50.55</v>
+        <v>23.59</v>
       </c>
       <c r="O6" t="n">
-        <v>853819433000</v>
+        <v>58427261200</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>325000</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-239000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스, 나스닥 선물 급락 및 반도체 시세 종료 우려 속 부정적 전망 지배적.</t>
+          <t>두산에너빌리티, 국제 유가 상승 및 한미 정부 지원 기대감으로 인한 상승 가능성 언급. 다만, 미국 원전주 폭락 소식은 부담.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['국제 유가', '원전주', '정부 지원']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>250500</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-3.47%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>762</v>
+      </c>
+      <c r="F7" t="n">
+        <v>479</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2385</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>259500</v>
+      </c>
+      <c r="K7" t="n">
+        <v>249500</v>
+      </c>
+      <c r="L7" t="n">
+        <v>251500</v>
+      </c>
+      <c r="M7" t="n">
+        <v>249000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="O7" t="n">
+        <v>626961200000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75900</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1023000</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>['나스닥 선물', '반도체 시세', '몰락']</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>삼성전자, 지정학적 리스크 및 AI 속도 조절론 속 외국인 매도세 동반 하락. 다만, 글로벌 증시 변동성과 연동되는 모습.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['지정학적 리스크', 'AI 속도론', '외국인 매도']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1719000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-5.13%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>476</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1560</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1192386069500</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>325000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-363000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>혼재된 전망 속 일부 호재 기대감 있으나, 시장 전반의 하락세 영향으로 부정적 기류 형성.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['반도체', '트럼프', '나스닥']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>70</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20260914_09.xlsx
+++ b/data/trending_integrated_20260914_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18050</v>
+        <v>7160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+12.39%</t>
+          <t>+29.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.31</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16060</v>
+        <v>5510</v>
       </c>
       <c r="K2" t="n">
-        <v>16780</v>
+        <v>5910</v>
       </c>
       <c r="L2" t="n">
-        <v>18610</v>
+        <v>7160</v>
       </c>
       <c r="M2" t="n">
-        <v>16230</v>
+        <v>5890</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>153877047085</v>
+        <v>25319128885</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>10360</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>2965</v>
       </c>
       <c r="R2" t="n">
-        <v>112000</v>
+        <v>-27000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 변동성 속에서, 사이버 보안 관련주의 부각 및 긍정적 주가 흐름 기대.</t>
+          <t>AI 보안 및 딥페이크 대장주로서의 기대감과 함께, 2등주, 3등주 움직임 및 보안주 전반의 흐름에 대한 관망세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '사이버 보안', '상승']</t>
+          <t>['AI 보안', '딥페이크', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8710</v>
+        <v>17690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+5.07%</t>
+          <t>+10.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.54</v>
+        <v>0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>0.75</v>
+        <v>2.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8290</v>
+        <v>16060</v>
       </c>
       <c r="K3" t="n">
-        <v>8100</v>
+        <v>16780</v>
       </c>
       <c r="L3" t="n">
-        <v>8900</v>
+        <v>18610</v>
       </c>
       <c r="M3" t="n">
-        <v>8060</v>
+        <v>16230</v>
       </c>
       <c r="N3" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="O3" t="n">
-        <v>8385544075</v>
+        <v>181080306020</v>
       </c>
       <c r="P3" t="n">
-        <v>21500</v>
+        <v>30550</v>
       </c>
       <c r="Q3" t="n">
-        <v>2300</v>
+        <v>6100</v>
       </c>
       <c r="R3" t="n">
-        <v>27000</v>
+        <v>112000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>항암 신약 관련 글로벌 심포지엄 개최 소식 기반, 투자주의 해제 후 상승 기대감 고조.</t>
+          <t>AI 개발 속도 조절론에 대한 상반된 해석 속 2연상 기대감과 양자 보안 관련주로서의 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['항암', '신약', '심포지엄']</t>
+          <t>['AI', '양자 보안', '2연상']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15150</v>
+        <v>8610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+3.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E4" t="n">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K4" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L4" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M4" t="n">
-        <v>15100</v>
+        <v>8060</v>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
-        <v>67030269340</v>
+        <v>13053120655</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제 유가 폭등 소식에 따른 상승 기대감.</t>
+          <t>암 치료 바이오 신약 관련 임상 결과 및 글로벌 심포지엄 개최 소식에 따른 기대감과 투자 주의 해제에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제 유가', '호르무즈 해협', '회담 연기']</t>
+          <t>['항암', '신약', '임상 결과']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14050</v>
+        <v>15150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+3.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>360</v>
       </c>
       <c r="H5" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K5" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L5" t="n">
-        <v>14310</v>
+        <v>16510</v>
       </c>
       <c r="M5" t="n">
-        <v>13800</v>
+        <v>15100</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
-        <v>19556056885</v>
+        <v>71150757755</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R5" t="n">
-        <v>24000</v>
+        <v>79000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>GPU 확보 관련 긍정 뉴스에 힘입어 기술력 부각, 프로그램 매수세 유입 기대감 존재.</t>
+          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제유가 폭등으로 인한 기대감 속에서 휴전, 협상, 합의 뉴스 시 하한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['GPU', '광통신', 'AIDC']</t>
+          <t>['국제유가', '호르무즈 해협', '회담 연기']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>88500</v>
+        <v>14200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>406</v>
+        <v>185</v>
       </c>
       <c r="H6" t="n">
-        <v>23.56</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>90800</v>
+        <v>14150</v>
       </c>
       <c r="K6" t="n">
-        <v>89800</v>
+        <v>13850</v>
       </c>
       <c r="L6" t="n">
-        <v>90400</v>
+        <v>14310</v>
       </c>
       <c r="M6" t="n">
-        <v>87800</v>
+        <v>13800</v>
       </c>
       <c r="N6" t="n">
-        <v>23.59</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>58427261200</v>
+        <v>24960874915</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>-239000</v>
+        <v>24000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 국제 유가 상승 및 한미 정부 지원 기대감으로 인한 상승 가능성 언급. 다만, 미국 원전주 폭락 소식은 부담.</t>
+          <t>AIDC 광통신 기술 성장 및 GPU 확보 관련 뉴스와 함께, 프로그램 매수세 유입에 대한 기대감과 광통신 종목 간 비교.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['국제 유가', '원전주', '정부 지원']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250500</v>
+        <v>88300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.47%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>762</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>2385</v>
+        <v>422</v>
       </c>
       <c r="H7" t="n">
-        <v>46.64</v>
+        <v>23.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>259500</v>
+        <v>90800</v>
       </c>
       <c r="K7" t="n">
-        <v>249500</v>
+        <v>89800</v>
       </c>
       <c r="L7" t="n">
-        <v>251500</v>
+        <v>90400</v>
       </c>
       <c r="M7" t="n">
-        <v>249000</v>
+        <v>87800</v>
       </c>
       <c r="N7" t="n">
-        <v>46.71</v>
+        <v>23.59</v>
       </c>
       <c r="O7" t="n">
-        <v>626961200000</v>
+        <v>66368627550</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>75900</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>-1023000</v>
+        <v>-239000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 지정학적 리스크 및 AI 속도 조절론 속 외국인 매도세 동반 하락. 다만, 글로벌 증시 변동성과 연동되는 모습.</t>
+          <t>두산에너빌리티, 국제 유가 상승 및 한미 정부 지원 기대감으로 인한 상승 가능성 언급. 다만, 미국 원전주 폭락 소식은 부담.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', 'AI 속도론', '외국인 매도']</t>
+          <t>['국제 유가', '원전주', '정부 지원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1719000</v>
+        <v>251500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-5.13%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="G8" t="n">
-        <v>1560</v>
+        <v>2293</v>
       </c>
       <c r="H8" t="n">
-        <v>50.47</v>
+        <v>46.64</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1812000</v>
+        <v>259500</v>
       </c>
       <c r="K8" t="n">
-        <v>1707000</v>
+        <v>249500</v>
       </c>
       <c r="L8" t="n">
-        <v>1729000</v>
+        <v>252000</v>
       </c>
       <c r="M8" t="n">
-        <v>1707000</v>
+        <v>249000</v>
       </c>
       <c r="N8" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="O8" t="n">
-        <v>1192386069500</v>
+        <v>725286779500</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>325000</v>
+        <v>75900</v>
       </c>
       <c r="R8" t="n">
-        <v>-363000</v>
+        <v>-1023000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>혼재된 전망 속 일부 호재 기대감 있으나, 시장 전반의 하락세 영향으로 부정적 기류 형성.</t>
+          <t>이란발 호재 및 나스닥 선물 급반등 소식에 대한 기대감과 HBM 관련 중국 추격에 대한 우려 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,18 +1187,110 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '트럼프', '나스닥']</t>
+          <t>['HBM', 'AI', '나스닥']</t>
         </is>
       </c>
       <c r="X8" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1718000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-5.19%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>485</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1469</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1435720710000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>325000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-363000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>반도체 주식 시세 종료 및 몰락 시작에 대한 부정적 전망과 자사주 매입 소식.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['반도체', '자사주 매입', '몰락']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>70</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20260914_09.xlsx
+++ b/data/trending_integrated_20260914_09.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7160</v>
+        <v>6810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.95%</t>
+          <t>+23.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H2" t="n">
         <v>1.67</v>
@@ -610,7 +610,7 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>25319128885</v>
+        <v>30879138595</v>
       </c>
       <c r="P2" t="n">
         <v>10360</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 대장주로서의 기대감과 함께, 2등주, 3등주 움직임 및 보안주 전반의 흐름에 대한 관망세.</t>
+          <t>AI 보안 및 딥페이크 관련주로 분류, 일부 상승 기대감 존재. 그러나 뚜렷한 호재는 부족.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 보안', '딥페이크', '대장주']</t>
+          <t>['AI보안', '딥페이크', '상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17690</v>
+        <v>17230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+10.15%</t>
+          <t>+7.29%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
@@ -702,7 +702,7 @@
         <v>2.39</v>
       </c>
       <c r="O3" t="n">
-        <v>181080306020</v>
+        <v>197183471800</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 대한 상반된 해석 속 2연상 기대감과 양자 보안 관련주로서의 부각.</t>
+          <t>AI 속도 조절론 속 양자 보안 테마 상승 기대감. 일부 투자자는 높은 수익률 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI', '양자 보안', '2연상']</t>
+          <t>['AI', '양자보안', '상승']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8610</v>
+        <v>15110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+3.86%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.54</v>
+        <v>-1.97</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8290</v>
+        <v>14610</v>
       </c>
       <c r="K4" t="n">
-        <v>8100</v>
+        <v>15420</v>
       </c>
       <c r="L4" t="n">
-        <v>9050</v>
+        <v>16510</v>
       </c>
       <c r="M4" t="n">
-        <v>8060</v>
+        <v>15050</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="O4" t="n">
-        <v>13053120655</v>
+        <v>74256557480</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>27000</v>
+        <v>79000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 관련 임상 결과 및 글로벌 심포지엄 개최 소식에 따른 기대감과 투자 주의 해제에 대한 긍정적 전망.</t>
+          <t>이란-걸프 국가 회담 연기 및 국제 유가 폭등 관련 분석. 단기적 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['항암', '신약', '임상 결과']</t>
+          <t>['국제유가', '호르무즈', '폭등']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15150</v>
+        <v>8400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K5" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L5" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M5" t="n">
-        <v>15100</v>
+        <v>8060</v>
       </c>
       <c r="N5" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
-        <v>71150757755</v>
+        <v>14976835075</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제유가 폭등으로 인한 기대감 속에서 휴전, 협상, 합의 뉴스 시 하한가 가능성 언급.</t>
+          <t>항암 신약 임상 결과 및 글로벌 심포지엄 개최로 인한 기대감. 투자 주의 해제 후 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈 해협', '회담 연기']</t>
+          <t>['항암', '신약', '임상']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14200</v>
+        <v>14320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="H6" t="n">
         <v>1.88</v>
@@ -969,7 +969,7 @@
         <v>13850</v>
       </c>
       <c r="L6" t="n">
-        <v>14310</v>
+        <v>14500</v>
       </c>
       <c r="M6" t="n">
         <v>13800</v>
@@ -978,7 +978,7 @@
         <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>24960874915</v>
+        <v>40175741850</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 성장 및 GPU 확보 관련 뉴스와 함께, 프로그램 매수세 유입에 대한 기대감과 광통신 종목 간 비교.</t>
+          <t>AIDC 광통신 기술 부각과 함께 주가 상승 기대감. 일부 투자자는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['광통신', 'AIDC', '기술력']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88300</v>
+        <v>88500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="H7" t="n">
         <v>23.56</v>
@@ -1070,7 +1070,7 @@
         <v>23.59</v>
       </c>
       <c r="O7" t="n">
-        <v>66368627550</v>
+        <v>75966321550</v>
       </c>
       <c r="P7" t="n">
         <v>139200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 국제 유가 상승 및 한미 정부 지원 기대감으로 인한 상승 가능성 언급. 다만, 미국 원전주 폭락 소식은 부담.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 기관 매집 및 공매도 세력과의 공방 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['국제 유가', '원전주', '정부 지원']</t>
+          <t>['국제유가', '원전주', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>251500</v>
+        <v>251000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="G8" t="n">
-        <v>2293</v>
+        <v>1993</v>
       </c>
       <c r="H8" t="n">
         <v>46.64</v>
@@ -1153,7 +1153,7 @@
         <v>249500</v>
       </c>
       <c r="L8" t="n">
-        <v>252000</v>
+        <v>252500</v>
       </c>
       <c r="M8" t="n">
         <v>249000</v>
@@ -1162,7 +1162,7 @@
         <v>46.71</v>
       </c>
       <c r="O8" t="n">
-        <v>725286779500</v>
+        <v>827443504750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이란발 호재 및 나스닥 선물 급반등 소식에 대한 기대감과 HBM 관련 중국 추격에 대한 우려 혼재.</t>
+          <t>AI 속도론에 따른 경쟁 심화 우려와 정치적 변수 언급. 일부 투자자는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM', 'AI', '나스닥']</t>
+          <t>['AI', '반도체', '중국']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1718000</v>
+        <v>1711000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-5.57%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="G9" t="n">
-        <v>1469</v>
+        <v>1445</v>
       </c>
       <c r="H9" t="n">
         <v>50.47</v>
@@ -1254,7 +1254,7 @@
         <v>50.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1435720710000</v>
+        <v>1686716528500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 주식 시세 종료 및 몰락 시작에 대한 부정적 전망과 자사주 매입 소식.</t>
+          <t>반도체 산업 몰락 및 주가 하락 전망. 투자자간 매도/매수 의견 대립.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '자사주 매입', '몰락']</t>
+          <t>['반도체', '주가', '매수']</t>
         </is>
       </c>
       <c r="X9" t="n">

--- a/data/trending_integrated_20260914_09.xlsx
+++ b/data/trending_integrated_20260914_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6810</v>
+        <v>6740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.59%</t>
+          <t>+58.78%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>1.67</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5510</v>
+        <v>4245</v>
       </c>
       <c r="K2" t="n">
-        <v>5910</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>7160</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5890</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>30879138595</v>
+        <v>37452000000</v>
       </c>
       <c r="P2" t="n">
-        <v>10360</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2965</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-27000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 관련주로 분류, 일부 상승 기대감 존재. 그러나 뚜렷한 호재는 부족.</t>
+          <t>AI 보안 및 딥페이크 대장주 관련 논의. 샌즈랩, 씨이랩 등 언급 및 보안주 상승 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI보안', '딥페이크', '상승']</t>
+          <t>['AI 보안', '딥페이크', '보안주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.31</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
@@ -702,7 +702,7 @@
         <v>2.39</v>
       </c>
       <c r="O3" t="n">
-        <v>197183471800</v>
+        <v>208047433170</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 속도 조절론 속 양자 보안 테마 상승 기대감. 일부 투자자는 높은 수익률 언급.</t>
+          <t>AI 개발 속도 조절론 관련 변동성. 양자 보안 테마로 2연상 기대감 및 매물대 정리 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI', '양자보안', '상승']</t>
+          <t>['AI 개발', '양자 보안', '매물대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15110</v>
+        <v>8470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.97</v>
+        <v>-0.54</v>
       </c>
       <c r="E4" t="n">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>371</v>
+        <v>448</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14610</v>
+        <v>8290</v>
       </c>
       <c r="K4" t="n">
-        <v>15420</v>
+        <v>8100</v>
       </c>
       <c r="L4" t="n">
-        <v>16510</v>
+        <v>9050</v>
       </c>
       <c r="M4" t="n">
-        <v>15050</v>
+        <v>8060</v>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
-        <v>74256557480</v>
+        <v>15665238085</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이란-걸프 국가 회담 연기 및 국제 유가 폭등 관련 분석. 단기적 상승 가능성 언급.</t>
+          <t>항암 신약 임상 결과 기대감 및 글로벌 심포지엄 개최. 투자주의 해제 후 주가 상승 모멘텀 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '폭등']</t>
+          <t>['항암 신약', '임상 결과', '심포지엄']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8400</v>
+        <v>14360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>405</v>
+        <v>230</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8290</v>
+        <v>14150</v>
       </c>
       <c r="K5" t="n">
-        <v>8100</v>
+        <v>13850</v>
       </c>
       <c r="L5" t="n">
-        <v>9050</v>
+        <v>14530</v>
       </c>
       <c r="M5" t="n">
-        <v>8060</v>
+        <v>13800</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>14976835075</v>
+        <v>49650898270</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>27000</v>
+        <v>24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>항암 신약 임상 결과 및 글로벌 심포지엄 개최로 인한 기대감. 투자 주의 해제 후 상승 전망.</t>
+          <t>AIDC 광통신 기술 및 GPU 확보 관련 긍정적 전망. AI 속도 조절론 언급 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['항암', '신약', '임상']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14320</v>
+        <v>14810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
-        <v>214</v>
+        <v>383</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K6" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L6" t="n">
-        <v>14500</v>
+        <v>16510</v>
       </c>
       <c r="M6" t="n">
-        <v>13800</v>
+        <v>14800</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O6" t="n">
-        <v>40175741850</v>
+        <v>78493185455</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R6" t="n">
-        <v>24000</v>
+        <v>79000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 부각과 함께 주가 상승 기대감. 일부 투자자는 매도 의견 제시.</t>
+          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제유가 폭등 관련 주가 상승 기대감. 휴전, 협상 뉴스 시 하한가 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '기술력']</t>
+          <t>['국제유가', '호르무즈 해협', '회담 연기']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88500</v>
+        <v>88800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-2.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="H7" t="n">
         <v>23.56</v>
@@ -1070,7 +1070,7 @@
         <v>23.59</v>
       </c>
       <c r="O7" t="n">
-        <v>75966321550</v>
+        <v>81970372050</v>
       </c>
       <c r="P7" t="n">
         <v>139200</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>251000</v>
+        <v>12100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>502</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>1993</v>
+        <v>71</v>
       </c>
       <c r="H8" t="n">
-        <v>46.64</v>
+        <v>17.58</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>259500</v>
+        <v>12450</v>
       </c>
       <c r="K8" t="n">
-        <v>249500</v>
+        <v>11960</v>
       </c>
       <c r="L8" t="n">
-        <v>252500</v>
+        <v>13900</v>
       </c>
       <c r="M8" t="n">
-        <v>249000</v>
+        <v>11890</v>
       </c>
       <c r="N8" t="n">
-        <v>46.71</v>
+        <v>17.07</v>
       </c>
       <c r="O8" t="n">
-        <v>827443504750</v>
+        <v>44854567400</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>14350</v>
       </c>
       <c r="Q8" t="n">
-        <v>75900</v>
+        <v>465</v>
       </c>
       <c r="R8" t="n">
-        <v>-1023000</v>
+        <v>187000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 속도론에 따른 경쟁 심화 우려와 정치적 변수 언급. 일부 투자자는 매도 의견 제시.</t>
+          <t>거래량 급증 및 상한가 기대감 속 외인 매도세 확인. 금호건설과의 연관성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '중국']</t>
+          <t>['거래량', '외인 매수', '금호건설']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1711000</v>
+        <v>252000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>1445</v>
+        <v>1870</v>
       </c>
       <c r="H9" t="n">
-        <v>50.47</v>
+        <v>46.64</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1812000</v>
+        <v>259500</v>
       </c>
       <c r="K9" t="n">
-        <v>1707000</v>
+        <v>249500</v>
       </c>
       <c r="L9" t="n">
-        <v>1729000</v>
+        <v>252500</v>
       </c>
       <c r="M9" t="n">
-        <v>1707000</v>
+        <v>249000</v>
       </c>
       <c r="N9" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="O9" t="n">
-        <v>1686716528500</v>
+        <v>897136706750</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>325000</v>
+        <v>75900</v>
       </c>
       <c r="R9" t="n">
-        <v>-363000</v>
+        <v>-1023000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 산업 몰락 및 주가 하락 전망. 투자자간 매도/매수 의견 대립.</t>
+          <t>나스닥 선물 변동성 및 정치적 이슈 언급. 반도체 산업 전망에 대한 부정적 시각 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,18 +1279,202 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '주가', '매수']</t>
+          <t>['나스닥 선물', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X9" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14035</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-4.59%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G10" t="n">
+        <v>117</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>14710</v>
+      </c>
+      <c r="K10" t="n">
+        <v>14710</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15420</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13900</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>18645758065</v>
+      </c>
+      <c r="P10" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>수원 파장1구역 재건축 시공사 선정 공시. 주가 하락 및 부정적 전망 상존.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['재건축', '시공사 선정', '공시']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1719000</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-5.13%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>800</v>
+      </c>
+      <c r="F11" t="n">
+        <v>486</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1370</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1867806981000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>325000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-363000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>반도체 산업 몰락 및 공매도 관련 부정적 의견. 자사주 매입 진행 중이나 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['반도체', '공매도', '자사주 매입']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>70</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
